--- a/quizzes/015_threat_modeling_quiz--quizzes.xlsx
+++ b/quizzes/015_threat_modeling_quiz--quizzes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>threat modelin practice</t>
+          <t>Threat Modeling Method Prac</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>threat modelin practice</t>
+          <t>Threat Modeling Practice</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>threat modelin practice</t>
+          <t>Threat Modeling Concept Prac</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>threat_modeling_concept_prac</t>
+          <t>threat_modeling_concept_prac_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>threat modelin practice</t>
+          <t>Threat Modeling Concept Prac 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>threat_modeling_concept_prac</t>
+          <t>threat_modeling_concept_prac_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>threat modelin practice</t>
+          <t>Threat Modeling Concept Prac 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>risk practic</t>
+          <t>Risk Level Prac</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -993,7 +993,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>threat_modeling_concept_prac</t>
+          <t>threat_modeling_concept_prac_4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>defense in practic</t>
+          <t>Defense In Breadth Prac</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>threat modelin practic</t>
+          <t>Threat Modeling Ess</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>threat modelin practic</t>
+          <t>Threat Modeling Prac</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
